--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-procedure-transport-Professionnel.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-procedure-transport-Professionnel.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5900" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5900" uniqueCount="676">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Cette entrée de type act permet de décrire le transport d'un professionnel lors d’un déplacement.</t>
+    <t>FrProcedureTransportProfessionnel permet de décrire le transport d'un professionnel lors d’un déplacement.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -459,10 +459,10 @@
 </t>
   </si>
   <si>
-    <t>Fr Autres Precision</t>
-  </si>
-  <si>
-    <t>Autres précision sur le trajet ou le transport du patient.</t>
+    <t>Extension - Fr Autres Precision</t>
+  </si>
+  <si>
+    <t>Extension permettant d'indiquer les autres précision sur le trajet ou le transport du patient.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -805,7 +805,10 @@
 </t>
   </si>
   <si>
-    <t>Qualifier du code</t>
+    <t>Extension - Qualifier du code</t>
+  </si>
+  <si>
+    <t>Extension permettant d’associer à un code une précision (qualifier).</t>
   </si>
   <si>
     <t>Procedure.code.coding.extension:qualifier.id</t>
@@ -1796,7 +1799,7 @@
 </t>
   </si>
   <si>
-    <t>Fr Lieu de départ du transport</t>
+    <t>Extension - Fr Lieu de départ du transport</t>
   </si>
   <si>
     <t>Extension pour représenter le lieu de départ d’un transport (patient ou professionnel).</t>
@@ -5351,7 +5354,7 @@
         <v>252</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>134</v>
+        <v>253</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5431,10 +5434,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5543,10 +5546,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5554,7 +5557,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>79</v>
@@ -5655,13 +5658,13 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>77</v>
@@ -5769,10 +5772,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5881,10 +5884,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5993,10 +5996,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6022,13 +6025,13 @@
         <v>101</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6036,7 +6039,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>77</v>
@@ -6078,7 +6081,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>87</v>
@@ -6107,10 +6110,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6136,10 +6139,10 @@
         <v>200</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6151,7 +6154,7 @@
         <v>77</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>77</v>
@@ -6190,7 +6193,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6219,13 +6222,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>77</v>
@@ -6333,10 +6336,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6445,10 +6448,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6557,10 +6560,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6586,13 +6589,13 @@
         <v>101</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6600,7 +6603,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>77</v>
@@ -6642,7 +6645,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>87</v>
@@ -6671,10 +6674,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6700,10 +6703,10 @@
         <v>200</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6754,7 +6757,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6783,10 +6786,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6895,10 +6898,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7009,10 +7012,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7125,10 +7128,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7237,10 +7240,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7351,10 +7354,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7380,16 +7383,16 @@
         <v>101</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -7418,7 +7421,7 @@
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
@@ -7436,7 +7439,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7454,21 +7457,21 @@
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7494,13 +7497,13 @@
         <v>228</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7550,7 +7553,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7568,21 +7571,21 @@
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7608,14 +7611,14 @@
         <v>107</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -7664,7 +7667,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7682,21 +7685,21 @@
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7722,14 +7725,14 @@
         <v>228</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7778,7 +7781,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7796,21 +7799,21 @@
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7833,19 +7836,19 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7894,7 +7897,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7912,21 +7915,21 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7952,16 +7955,16 @@
         <v>228</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -8010,7 +8013,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -8028,21 +8031,21 @@
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8068,13 +8071,13 @@
         <v>101</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8082,7 +8085,7 @@
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>77</v>
@@ -8124,7 +8127,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>87</v>
@@ -8153,10 +8156,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8179,13 +8182,13 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8236,7 +8239,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8265,10 +8268,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8294,16 +8297,16 @@
         <v>101</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -8352,7 +8355,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8370,21 +8373,21 @@
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8410,13 +8413,13 @@
         <v>228</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8466,7 +8469,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8484,21 +8487,21 @@
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8524,14 +8527,14 @@
         <v>107</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -8580,7 +8583,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8598,21 +8601,21 @@
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8638,14 +8641,14 @@
         <v>228</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -8694,7 +8697,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8712,21 +8715,21 @@
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8749,19 +8752,19 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -8810,7 +8813,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8828,21 +8831,21 @@
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8868,16 +8871,16 @@
         <v>228</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8926,7 +8929,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8944,25 +8947,25 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8981,13 +8984,13 @@
         <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9038,7 +9041,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>87</v>
@@ -9053,24 +9056,24 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9093,16 +9096,16 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9152,7 +9155,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9167,24 +9170,24 @@
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9207,16 +9210,16 @@
         <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9254,17 +9257,17 @@
         <v>77</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AC60" s="2"/>
       <c r="AD60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9279,27 +9282,27 @@
         <v>99</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>77</v>
@@ -9321,16 +9324,16 @@
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9380,7 +9383,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9395,24 +9398,24 @@
         <v>99</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9435,13 +9438,13 @@
         <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9492,7 +9495,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9510,10 +9513,10 @@
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>77</v>
@@ -9521,10 +9524,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9547,13 +9550,13 @@
         <v>88</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9604,7 +9607,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9622,10 +9625,10 @@
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>77</v>
@@ -9633,10 +9636,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9659,13 +9662,13 @@
         <v>88</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9716,7 +9719,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9731,10 +9734,10 @@
         <v>99</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
@@ -9745,10 +9748,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9857,10 +9860,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9971,14 +9974,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10000,10 +10003,10 @@
         <v>132</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>149</v>
@@ -10058,7 +10061,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10087,10 +10090,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10116,14 +10119,14 @@
         <v>200</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -10151,10 +10154,10 @@
         <v>204</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>77</v>
@@ -10172,7 +10175,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10187,24 +10190,24 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10227,17 +10230,17 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>77</v>
@@ -10286,7 +10289,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>87</v>
@@ -10301,24 +10304,24 @@
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10427,10 +10430,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10539,13 +10542,13 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="B72" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="B72" t="s" s="2">
-        <v>432</v>
-      </c>
       <c r="C72" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D72" t="s" s="2">
         <v>77</v>
@@ -10567,13 +10570,13 @@
         <v>77</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10653,10 +10656,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10765,10 +10768,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10776,7 +10779,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>79</v>
@@ -10877,13 +10880,13 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B75" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="B75" t="s" s="2">
-        <v>441</v>
-      </c>
       <c r="C75" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>77</v>
@@ -10991,10 +10994,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11103,10 +11106,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11215,10 +11218,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11244,13 +11247,13 @@
         <v>101</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11258,7 +11261,7 @@
       </c>
       <c r="Q78" s="2"/>
       <c r="R78" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="S78" t="s" s="2">
         <v>77</v>
@@ -11300,7 +11303,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>87</v>
@@ -11329,10 +11332,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11358,10 +11361,10 @@
         <v>107</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11370,7 +11373,7 @@
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="S79" t="s" s="2">
         <v>77</v>
@@ -11392,7 +11395,7 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>77</v>
@@ -11410,7 +11413,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11439,13 +11442,13 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>77</v>
@@ -11553,10 +11556,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11665,10 +11668,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11777,10 +11780,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11806,13 +11809,13 @@
         <v>101</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11820,7 +11823,7 @@
       </c>
       <c r="Q83" s="2"/>
       <c r="R83" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="S83" t="s" s="2">
         <v>77</v>
@@ -11862,7 +11865,7 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>87</v>
@@ -11891,10 +11894,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11920,10 +11923,10 @@
         <v>200</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11974,7 +11977,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12003,10 +12006,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12115,10 +12118,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12229,10 +12232,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12345,10 +12348,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12457,10 +12460,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12571,10 +12574,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12600,16 +12603,16 @@
         <v>101</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>77</v>
@@ -12658,7 +12661,7 @@
         <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12676,21 +12679,21 @@
         <v>77</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12716,13 +12719,13 @@
         <v>228</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12772,7 +12775,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12790,21 +12793,21 @@
         <v>77</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12830,14 +12833,14 @@
         <v>107</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>77</v>
@@ -12847,7 +12850,7 @@
         <v>77</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>77</v>
@@ -12886,7 +12889,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -12904,21 +12907,21 @@
         <v>77</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12944,14 +12947,14 @@
         <v>228</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>77</v>
@@ -13000,7 +13003,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13018,21 +13021,21 @@
         <v>77</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13055,19 +13058,19 @@
         <v>88</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>77</v>
@@ -13116,7 +13119,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13134,21 +13137,21 @@
         <v>77</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13174,16 +13177,16 @@
         <v>228</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>77</v>
@@ -13232,7 +13235,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13250,24 +13253,24 @@
         <v>77</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>77</v>
@@ -13375,10 +13378,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13487,10 +13490,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13599,10 +13602,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13628,13 +13631,13 @@
         <v>101</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13642,7 +13645,7 @@
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>77</v>
@@ -13684,7 +13687,7 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>87</v>
@@ -13713,10 +13716,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13739,13 +13742,13 @@
         <v>77</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13796,7 +13799,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -13825,10 +13828,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13854,13 +13857,13 @@
         <v>101</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13868,7 +13871,7 @@
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>77</v>
@@ -13910,7 +13913,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>87</v>
@@ -13939,10 +13942,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13965,13 +13968,13 @@
         <v>77</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14022,7 +14025,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14051,13 +14054,13 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>77</v>
@@ -14079,13 +14082,13 @@
         <v>77</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14165,10 +14168,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14277,10 +14280,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14288,7 +14291,7 @@
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G105" t="s" s="2">
         <v>79</v>
@@ -14389,13 +14392,13 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D106" t="s" s="2">
         <v>77</v>
@@ -14503,10 +14506,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14615,10 +14618,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14727,10 +14730,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14756,13 +14759,13 @@
         <v>101</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -14770,7 +14773,7 @@
       </c>
       <c r="Q109" s="2"/>
       <c r="R109" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="S109" t="s" s="2">
         <v>77</v>
@@ -14812,7 +14815,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>87</v>
@@ -14841,10 +14844,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14870,10 +14873,10 @@
         <v>107</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -14882,7 +14885,7 @@
       </c>
       <c r="Q110" s="2"/>
       <c r="R110" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="S110" t="s" s="2">
         <v>77</v>
@@ -14904,7 +14907,7 @@
       </c>
       <c r="Y110" s="2"/>
       <c r="Z110" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>77</v>
@@ -14922,7 +14925,7 @@
         <v>77</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -14951,13 +14954,13 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>77</v>
@@ -15065,10 +15068,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15177,10 +15180,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15289,10 +15292,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15318,13 +15321,13 @@
         <v>101</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -15332,7 +15335,7 @@
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>77</v>
@@ -15374,7 +15377,7 @@
         <v>77</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>87</v>
@@ -15403,10 +15406,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15432,10 +15435,10 @@
         <v>200</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -15466,7 +15469,7 @@
       </c>
       <c r="Y115" s="2"/>
       <c r="Z115" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>77</v>
@@ -15484,7 +15487,7 @@
         <v>77</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -15513,10 +15516,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15625,10 +15628,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15739,10 +15742,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15855,10 +15858,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15967,10 +15970,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16081,10 +16084,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16110,16 +16113,16 @@
         <v>101</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>77</v>
@@ -16168,7 +16171,7 @@
         <v>77</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -16186,21 +16189,21 @@
         <v>77</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16226,13 +16229,13 @@
         <v>228</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -16282,7 +16285,7 @@
         <v>77</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -16300,21 +16303,21 @@
         <v>77</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16340,14 +16343,14 @@
         <v>107</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>77</v>
@@ -16357,7 +16360,7 @@
         <v>77</v>
       </c>
       <c r="S123" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="T123" t="s" s="2">
         <v>77</v>
@@ -16396,7 +16399,7 @@
         <v>77</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -16414,21 +16417,21 @@
         <v>77</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16454,14 +16457,14 @@
         <v>228</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>77</v>
@@ -16510,7 +16513,7 @@
         <v>77</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -16528,21 +16531,21 @@
         <v>77</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16565,19 +16568,19 @@
         <v>88</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>77</v>
@@ -16626,7 +16629,7 @@
         <v>77</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -16644,21 +16647,21 @@
         <v>77</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16684,16 +16687,16 @@
         <v>228</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>77</v>
@@ -16742,7 +16745,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -16760,24 +16763,24 @@
         <v>77</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D127" t="s" s="2">
         <v>77</v>
@@ -16885,10 +16888,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16997,10 +17000,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17109,10 +17112,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17138,13 +17141,13 @@
         <v>101</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
@@ -17152,7 +17155,7 @@
       </c>
       <c r="Q130" s="2"/>
       <c r="R130" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="S130" t="s" s="2">
         <v>77</v>
@@ -17194,7 +17197,7 @@
         <v>77</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>87</v>
@@ -17223,10 +17226,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17249,13 +17252,13 @@
         <v>77</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -17306,7 +17309,7 @@
         <v>77</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>78</v>
@@ -17335,10 +17338,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17364,13 +17367,13 @@
         <v>101</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -17378,7 +17381,7 @@
       </c>
       <c r="Q132" s="2"/>
       <c r="R132" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="S132" t="s" s="2">
         <v>77</v>
@@ -17420,7 +17423,7 @@
         <v>77</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>87</v>
@@ -17449,10 +17452,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17475,13 +17478,13 @@
         <v>77</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -17532,7 +17535,7 @@
         <v>77</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>78</v>
@@ -17561,10 +17564,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17590,13 +17593,13 @@
         <v>228</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -17646,7 +17649,7 @@
         <v>77</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>78</v>
@@ -17655,7 +17658,7 @@
         <v>87</v>
       </c>
       <c r="AI134" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AJ134" t="s" s="2">
         <v>99</v>
@@ -17675,10 +17678,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17704,13 +17707,13 @@
         <v>101</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -17736,13 +17739,13 @@
         <v>77</v>
       </c>
       <c r="X135" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Y135" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="Z135" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>77</v>
@@ -17760,7 +17763,7 @@
         <v>77</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -17789,10 +17792,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17818,13 +17821,13 @@
         <v>153</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -17874,7 +17877,7 @@
         <v>77</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>78</v>
@@ -17892,7 +17895,7 @@
         <v>77</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>77</v>
@@ -17903,10 +17906,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17932,13 +17935,13 @@
         <v>228</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -17988,7 +17991,7 @@
         <v>77</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>78</v>
@@ -18017,10 +18020,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18043,17 +18046,17 @@
         <v>77</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>77</v>
@@ -18102,7 +18105,7 @@
         <v>77</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>78</v>
@@ -18120,7 +18123,7 @@
         <v>77</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AM138" t="s" s="2">
         <v>77</v>
@@ -18131,10 +18134,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18157,17 +18160,17 @@
         <v>88</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>77</v>
@@ -18216,7 +18219,7 @@
         <v>77</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>78</v>
@@ -18234,10 +18237,10 @@
         <v>77</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>77</v>
@@ -18245,10 +18248,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18357,10 +18360,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18471,13 +18474,13 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="B142" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="B142" t="s" s="2">
-        <v>569</v>
-      </c>
       <c r="C142" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D142" t="s" s="2">
         <v>77</v>
@@ -18499,13 +18502,13 @@
         <v>77</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -18585,13 +18588,13 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D143" t="s" s="2">
         <v>77</v>
@@ -18613,13 +18616,13 @@
         <v>77</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -18699,10 +18702,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18728,13 +18731,13 @@
         <v>228</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -18784,7 +18787,7 @@
         <v>77</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>78</v>
@@ -18793,7 +18796,7 @@
         <v>87</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AJ144" t="s" s="2">
         <v>99</v>
@@ -18813,10 +18816,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18842,13 +18845,13 @@
         <v>101</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
@@ -18874,13 +18877,13 @@
         <v>77</v>
       </c>
       <c r="X145" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>77</v>
@@ -18898,7 +18901,7 @@
         <v>77</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>78</v>
@@ -18927,10 +18930,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -18956,13 +18959,13 @@
         <v>153</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
@@ -19012,7 +19015,7 @@
         <v>77</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>78</v>
@@ -19030,7 +19033,7 @@
         <v>77</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AM146" t="s" s="2">
         <v>77</v>
@@ -19041,10 +19044,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19070,13 +19073,13 @@
         <v>228</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -19126,7 +19129,7 @@
         <v>77</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>78</v>
@@ -19155,10 +19158,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19184,13 +19187,13 @@
         <v>200</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -19219,10 +19222,10 @@
         <v>204</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>77</v>
@@ -19240,7 +19243,7 @@
         <v>77</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>78</v>
@@ -19255,13 +19258,13 @@
         <v>99</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>77</v>
@@ -19269,10 +19272,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19295,16 +19298,16 @@
         <v>88</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -19354,7 +19357,7 @@
         <v>77</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>78</v>
@@ -19369,13 +19372,13 @@
         <v>99</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>77</v>
@@ -19383,10 +19386,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19412,13 +19415,13 @@
         <v>200</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -19447,10 +19450,10 @@
         <v>204</v>
       </c>
       <c r="Y150" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="Z150" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>77</v>
@@ -19468,7 +19471,7 @@
         <v>77</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>78</v>
@@ -19486,21 +19489,21 @@
         <v>77</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19526,13 +19529,13 @@
         <v>200</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -19561,10 +19564,10 @@
         <v>204</v>
       </c>
       <c r="Y151" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="Z151" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>77</v>
@@ -19582,7 +19585,7 @@
         <v>77</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>78</v>
@@ -19600,7 +19603,7 @@
         <v>77</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>77</v>
@@ -19611,10 +19614,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19637,16 +19640,16 @@
         <v>77</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -19696,7 +19699,7 @@
         <v>77</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>78</v>
@@ -19714,7 +19717,7 @@
         <v>77</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>77</v>
@@ -19725,10 +19728,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19754,13 +19757,13 @@
         <v>200</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -19789,10 +19792,10 @@
         <v>204</v>
       </c>
       <c r="Y153" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="Z153" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>77</v>
@@ -19810,7 +19813,7 @@
         <v>77</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>78</v>
@@ -19828,7 +19831,7 @@
         <v>77</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AM153" t="s" s="2">
         <v>77</v>
@@ -19839,10 +19842,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19865,17 +19868,17 @@
         <v>77</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>77</v>
@@ -19924,7 +19927,7 @@
         <v>77</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>78</v>
@@ -19942,7 +19945,7 @@
         <v>77</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AM154" t="s" s="2">
         <v>77</v>
@@ -19953,10 +19956,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -19982,10 +19985,10 @@
         <v>200</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -20015,10 +20018,10 @@
         <v>204</v>
       </c>
       <c r="Y155" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="Z155" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>77</v>
@@ -20036,7 +20039,7 @@
         <v>77</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>78</v>
@@ -20054,7 +20057,7 @@
         <v>77</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AM155" t="s" s="2">
         <v>77</v>
@@ -20065,10 +20068,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20091,13 +20094,13 @@
         <v>77</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -20148,7 +20151,7 @@
         <v>77</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>78</v>
@@ -20163,24 +20166,24 @@
         <v>99</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20203,13 +20206,13 @@
         <v>77</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -20260,7 +20263,7 @@
         <v>77</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>78</v>
@@ -20278,7 +20281,7 @@
         <v>77</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AM157" t="s" s="2">
         <v>77</v>
@@ -20289,10 +20292,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20401,10 +20404,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20515,14 +20518,14 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
@@ -20544,10 +20547,10 @@
         <v>132</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N160" t="s" s="2">
         <v>149</v>
@@ -20602,7 +20605,7 @@
         <v>77</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>78</v>
@@ -20631,10 +20634,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -20660,10 +20663,10 @@
         <v>200</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -20693,10 +20696,10 @@
         <v>111</v>
       </c>
       <c r="Y161" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="Z161" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>77</v>
@@ -20714,7 +20717,7 @@
         <v>77</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>78</v>
@@ -20732,7 +20735,7 @@
         <v>77</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AM161" t="s" s="2">
         <v>77</v>
@@ -20743,10 +20746,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -20769,13 +20772,13 @@
         <v>77</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -20826,7 +20829,7 @@
         <v>77</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>87</v>
@@ -20844,7 +20847,7 @@
         <v>77</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AM162" t="s" s="2">
         <v>77</v>
@@ -20855,10 +20858,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -20881,19 +20884,19 @@
         <v>77</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>77</v>
@@ -20942,7 +20945,7 @@
         <v>77</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>78</v>
@@ -20960,7 +20963,7 @@
         <v>77</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AM163" t="s" s="2">
         <v>77</v>
@@ -20971,10 +20974,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21000,13 +21003,13 @@
         <v>200</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -21035,10 +21038,10 @@
         <v>204</v>
       </c>
       <c r="Y164" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="Z164" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>77</v>
@@ -21056,7 +21059,7 @@
         <v>77</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>78</v>
@@ -21074,7 +21077,7 @@
         <v>77</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AM164" t="s" s="2">
         <v>77</v>
